--- a/cihifeedback/rowsWithSuggestedCode-stemCode-relationsAndRules.xlsx
+++ b/cihifeedback/rowsWithSuggestedCode-stemCode-relationsAndRules.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stem Codes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stem Codes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,13 +28,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDDDDD"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -48,9 +61,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,6 +439,730 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Mapping relations and proposed Foundation mapping rules: stem-code suggestions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Each row is a still-actionable CIHI feedback entry whose suggested ICD-11 code (column K) is a single MMS stem code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Step 4 adds the Foundation entity of that code (P), its relation to the ICD-10 source (U, V), a proposed Foundation mapping rule (W-AA) and a confidence grade (AB, AC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Rows: 337 (sheet 'Stem Codes'). Generated 2026-10-03 by bin/generateMappingRelationsAndRules.py using ICD-11 MMS 2026-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Columns A-T follow the WHO Mapping Feedback Template; columns U-AC are added by step 4. See doc/Method.md and doc/mappingRulesSpecification.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Possible values</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Organization/Affiliation</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Organization giving the feedback.</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>CIHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Date of CIHI's feedback.</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Contact person for the feedback.</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Sharon Baker</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Contact Details</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Contact address for the feedback.</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>whofic.mtf@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Version of WHO Mapping Table</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>WHO map that CIHI reviewed.</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2022 10To11MapToOneCategory</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Map direction</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Direction of the reviewed map.</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Forward (ICD-10 to ICD-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>WHO ICD-10 / ICD-11 Code</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>ICD-10 source code (S in the rules).</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>An ICD-10 code, e.g. A84.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>WHO ICD-10 / ICD-11 Code Title</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Title of the ICD-10 source code.</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>WHO Mapped ICD-10/ ICD-11 Code</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>ICD-11 MMS code that the WHO 2022 map assigns to the source.</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>An ICD-11 MMS code</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>WHO Mapped ICD-10 / ICD-11 Title</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Title of the WHO-mapped code.</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Suggested/Corrected Mapped ICD-10 /ICD-11 Code</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>CIHI's suggested ICD-11 code (T1 in the rules).</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>A single ICD-11 MMS stem code not ending in Y, e.g. 1C8G.Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Suggested/Corrected Mapped ICD-10 / ICD-11 Code Title</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Title of the suggested code.</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Empty (not filled for stem codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Corrected Code Mapping Relation</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>CIHI's relation of the suggested code (K) to the source, from CIHI's E/B/N assessment.</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Equivalent; Broader (target broader than source); Narrower (target narrower than source); empty = not assessed by CIHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Comments of the CIHI reviewers and conflict-resolution team.</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Free text, or empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>WHO Mapped Foundation Entity</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Foundation entity of the WHO-mapped code.</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Empty (not filled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Suggested/Corrected Mapped Foundation Entity</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Foundation entity of the suggested code (T1U). Residual categories (.Z) are mapped to the Foundation entity of their parent.</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>A Foundation URI, e.g. http://id.who.int/icd/entity/835129952</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>CIHI's reason why its map differs from WHO's.</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>NoMatch_2022CodingTool Guides to CIHI chosen map; NoMatch_2023CodingTool Guides to CIHI chosen map; NoMatch_Residual Y versus Z; NoMatch_Validator decision; NoMatch_1:many stem code map possible (...); NoMatch_WHO maps to category level; NoMatch_No WHO map available; or empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Action for WHO</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Action CIHI asks WHO to take. Only rows containing 'Update WHO map' or starting with 'Update map' get a mapping rule.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Mostly 'Update WHO map', sometimes with 'Add index term.', 'Review indexing.', 'Add postcoordination.' or 'See comment.'; occasionally other text (e.g. 'Review modelling.')</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Details of the requested action.</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Empty (not filled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Status of the feedback, for WHO to fill in.</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Completed Code Mapping Relation</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Relation of the suggested code (K) to the ICD-10 source: CIHI's relation (M) where present, otherwise inferred.</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Equivalent (same concept); Broader (target broader than source); Narrower (target narrower than source); Related (overlapping or different concepts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>How the relation in U was obtained.</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>'Manual' (copied from M); 'Rule n: ... Target: &lt;Foundation title&gt;' (rules of determine-stemcode-semantic-relationships.md); or 'Medical-knowledge check: &lt;reason&gt; (rules gave ...)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Descendant match (T2U)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>For Broader rows: the Foundation entity below T1U used as the rule target, i.e. a closer match to the source or the most specific broader ancestor of one.</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>A Foundation URI, or empty (rule uses T1U, or no rule)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Descendant match title</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Title of the descendant match.</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Text, or empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Descendant match relation</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Relation of the descendant match to the source.</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Equivalent; Broader; or empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Proposed mapping rule</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Proposed Foundation mapping rule for the ICD-10 source S. ≡: S is equivalent to the entity; ⊂: the entity is broader than S; ⊃: the entity is narrower than S.</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>'S ≡ URI', 'S ⊂ URI' or 'S ⊃ URI'; empty = no rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Rule notes</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>How the rule target was found, or why there is no rule.</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>e.g. 'T2 via Foundation search in T1U subtree'; '...reset to the most specific broader ancestor'; 'no match among T1U's descendants'; 'T1U has no descendants'; 'No rule: Action for WHO is ...'; 'No rule: ICD-10 source is an X.8 'other' residual'; 'No rule: relation is 'Related'; review'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Confidence in the proposed rule, or in the relation when there is no rule.</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>high; medium; low</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Confidence rationale</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Reasons for the confidence grade (see doc/Method.md, Confidence).</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AC338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
